--- a/uploads/feedback.xlsx
+++ b/uploads/feedback.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,10 +466,8 @@
           <t>asthasengar@gmail.com</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="C2" t="n">
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -479,6 +477,29 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>2025-07-09 22:24:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Astha sengar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>asthasengar2088@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-10-08 19:55:49</t>
         </is>
       </c>
     </row>
